--- a/Plannings 2026 S15.xlsx
+++ b/Plannings 2026 S15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F953700-6C2E-4E1D-8D1C-D14D7ADDDEA7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7944,7 +7944,7 @@
       <c r="F90" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G90" s="18" t="s">
+      <c r="G90" s="54" t="s">
         <v>59</v>
       </c>
       <c r="H90" s="19"/>
@@ -7962,7 +7962,7 @@
       <c r="F91" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G91" s="1" t="s">
+      <c r="G91" s="55" t="s">
         <v>117</v>
       </c>
       <c r="H91" s="26"/>
@@ -8843,13 +8843,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{744CE1F1-CD27-4266-9A98-F6C54EF8FFEE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A34CDE22-8465-4659-8521-E79C5228AA8B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F41EB0-F4AF-4816-9163-6C8ADF105326}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D1212E9-822A-401C-B398-ABE0B3D00853}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D7E64A4-E99B-45E4-820F-4A2C57506F77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD621067-9B7A-44C8-9D5B-AA32B358918C}"/>
 </file>
--- a/Plannings 2026 S15.xlsx
+++ b/Plannings 2026 S15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F953700-6C2E-4E1D-8D1C-D14D7ADDDEA7}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E3C082B-4D13-4A71-87F5-FE6456285F1B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="146">
   <si>
     <t>Planning des salariés du 06/04/2026 au 12/04/2026</t>
   </si>
@@ -457,6 +457,9 @@
   </si>
   <si>
     <t>P100M // EDF // ANNIV</t>
+  </si>
+  <si>
+    <t>11:00/13:00</t>
   </si>
 </sst>
 </file>
@@ -466,7 +469,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -565,6 +568,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -609,7 +618,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -851,11 +860,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1029,6 +1051,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5326,13 +5354,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5350,94 +5378,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5469,10 +5409,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5500,23 +5440,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>85</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5544,111 +5484,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5676,260 +5616,304 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>93</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5942,17 +5926,61 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
         <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
@@ -5986,13 +6014,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6237,6 +6265,94 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5743575" y="11049000"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="126" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39C2D579-1616-4A85-BE47-DAD747AE6A8D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19920857" y="13620750"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="127" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59FB2FAE-90D7-440E-A9EF-9EE92D31511D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13280571" y="14409964"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6618,7 +6734,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="49.7109375" customWidth="1"/>
@@ -7812,254 +7928,278 @@
       <c r="D80" s="18"/>
       <c r="E80" s="18"/>
       <c r="F80" s="18"/>
-      <c r="G80" s="54" t="s">
-        <v>59</v>
+      <c r="G80" s="18" t="s">
+        <v>16</v>
       </c>
       <c r="H80" s="19"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="25"/>
-      <c r="B81" s="1"/>
+      <c r="A81" s="61"/>
+      <c r="B81" s="27"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="55" t="s">
-        <v>89</v>
+      <c r="G81" s="62" t="s">
+        <v>145</v>
       </c>
       <c r="H81" s="26"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="25"/>
-      <c r="B82" s="1"/>
+      <c r="A82" s="61"/>
+      <c r="B82" s="27"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="2" t="s">
-        <v>16</v>
+      <c r="G82" s="52" t="s">
+        <v>59</v>
       </c>
       <c r="H82" s="26"/>
     </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="28"/>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="25"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
-      <c r="G83" s="1" t="s">
+      <c r="G83" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="H83" s="26"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="25"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H84" s="26"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="28"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H83" s="26"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="E84" s="18"/>
-      <c r="F84" s="18"/>
-      <c r="G84" s="18"/>
-      <c r="H84" s="19"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="20"/>
-      <c r="B85" s="22"/>
-      <c r="C85" s="22"/>
-      <c r="D85" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="E85" s="22"/>
-      <c r="F85" s="22"/>
-      <c r="G85" s="22"/>
-      <c r="H85" s="23"/>
+      <c r="H85" s="26"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B86" s="17"/>
       <c r="C86" s="18"/>
-      <c r="D86" s="18"/>
+      <c r="D86" s="34" t="s">
+        <v>12</v>
+      </c>
       <c r="E86" s="18"/>
       <c r="F86" s="18"/>
-      <c r="G86" s="34" t="s">
+      <c r="G86" s="18"/>
+      <c r="H86" s="19"/>
+    </row>
+    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="20"/>
+      <c r="B87" s="22"/>
+      <c r="C87" s="22"/>
+      <c r="D87" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="E87" s="22"/>
+      <c r="F87" s="22"/>
+      <c r="G87" s="22"/>
+      <c r="H87" s="23"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B88" s="17"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="18"/>
+      <c r="E88" s="18"/>
+      <c r="F88" s="18"/>
+      <c r="G88" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="H86" s="19"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="25"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="35" t="s">
+      <c r="H88" s="19"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="25"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="H87" s="26"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="25"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="37" t="s">
+      <c r="H89" s="26"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="25"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="H88" s="26"/>
-    </row>
-    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="20"/>
-      <c r="B89" s="22"/>
-      <c r="C89" s="22"/>
-      <c r="D89" s="22"/>
-      <c r="E89" s="22"/>
-      <c r="F89" s="22"/>
-      <c r="G89" s="41" t="s">
+      <c r="H90" s="26"/>
+    </row>
+    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="20"/>
+      <c r="B91" s="22"/>
+      <c r="C91" s="22"/>
+      <c r="D91" s="22"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="22"/>
+      <c r="G91" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="H89" s="23"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="16" t="s">
+      <c r="H91" s="23"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="B90" s="17"/>
-      <c r="C90" s="34" t="s">
+      <c r="B92" s="17"/>
+      <c r="C92" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D90" s="18" t="s">
+      <c r="D92" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E90" s="18"/>
-      <c r="F90" s="18" t="s">
+      <c r="E92" s="18"/>
+      <c r="F92" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G90" s="54" t="s">
+      <c r="G92" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="H90" s="19"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="25"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="35" t="s">
+      <c r="H92" s="19"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="25"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1" t="s">
+      <c r="E93" s="1"/>
+      <c r="F93" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G91" s="55" t="s">
+      <c r="G93" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="H91" s="26"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="25"/>
-      <c r="B92" s="1"/>
-      <c r="C92" s="2" t="s">
+      <c r="H93" s="26"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="25"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="2" t="s">
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H92" s="26"/>
-    </row>
-    <row r="93" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="20"/>
-      <c r="B93" s="22"/>
-      <c r="C93" s="22" t="s">
+      <c r="H94" s="26"/>
+    </row>
+    <row r="95" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="20"/>
+      <c r="B95" s="22"/>
+      <c r="C95" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="D93" s="22"/>
-      <c r="E93" s="22"/>
-      <c r="F93" s="22"/>
-      <c r="G93" s="22" t="s">
+      <c r="D95" s="22"/>
+      <c r="E95" s="22"/>
+      <c r="F95" s="22"/>
+      <c r="G95" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="H93" s="23"/>
-    </row>
-    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="24" t="s">
+      <c r="H95" s="23"/>
+    </row>
+    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="B94" s="31"/>
-      <c r="C94" s="30"/>
-      <c r="D94" s="30"/>
-      <c r="E94" s="30"/>
-      <c r="F94" s="30"/>
-      <c r="G94" s="30"/>
-      <c r="H94" s="32"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="16" t="s">
+      <c r="B96" s="31"/>
+      <c r="C96" s="30"/>
+      <c r="D96" s="30"/>
+      <c r="E96" s="30"/>
+      <c r="F96" s="30"/>
+      <c r="G96" s="30"/>
+      <c r="H96" s="32"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B95" s="17"/>
-      <c r="C95" s="18"/>
-      <c r="D95" s="34" t="s">
+      <c r="B97" s="17"/>
+      <c r="C97" s="18"/>
+      <c r="D97" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="E95" s="18"/>
-      <c r="F95" s="18"/>
-      <c r="G95" s="18"/>
-      <c r="H95" s="19"/>
-    </row>
-    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="20"/>
-      <c r="B96" s="22"/>
-      <c r="C96" s="22"/>
-      <c r="D96" s="41" t="s">
+      <c r="E97" s="18"/>
+      <c r="F97" s="18"/>
+      <c r="G97" s="18"/>
+      <c r="H97" s="19"/>
+    </row>
+    <row r="98" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="20"/>
+      <c r="B98" s="22"/>
+      <c r="C98" s="22"/>
+      <c r="D98" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="E96" s="22"/>
-      <c r="F96" s="22"/>
-      <c r="G96" s="22"/>
-      <c r="H96" s="23"/>
-    </row>
-    <row r="97" spans="2:8" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="33"/>
-      <c r="C97" s="33"/>
-      <c r="D97" s="33"/>
-      <c r="E97" s="33"/>
-      <c r="F97" s="33"/>
-      <c r="G97" s="33"/>
-      <c r="H97" s="33"/>
+      <c r="E98" s="22"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="22"/>
+      <c r="H98" s="23"/>
+    </row>
+    <row r="99" spans="1:8" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="33"/>
+      <c r="C99" s="33"/>
+      <c r="D99" s="33"/>
+      <c r="E99" s="33"/>
+      <c r="F99" s="33"/>
+      <c r="G99" s="33"/>
+      <c r="H99" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B97:H97"/>
+    <mergeCell ref="B99:H99"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="B47:H47"/>
     <mergeCell ref="B46:H46"/>
     <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B94:H94"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B96:H96"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A91"/>
+    <mergeCell ref="A92:A95"/>
+    <mergeCell ref="A97:A98"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A64:A71"/>
     <mergeCell ref="A72:A73"/>
     <mergeCell ref="A74:A79"/>
-    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A80:A85"/>
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="A50:A53"/>
     <mergeCell ref="A54:A61"/>
@@ -8843,13 +8983,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A34CDE22-8465-4659-8521-E79C5228AA8B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDAB798-0440-4850-BA72-F263CA81D953}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D1212E9-822A-401C-B398-ABE0B3D00853}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D713C6A8-9D75-4CA0-8563-0A53F6E83FDA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD621067-9B7A-44C8-9D5B-AA32B358918C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13671726-3036-4FB6-B875-2A77F871B70F}"/>
 </file>
--- a/Plannings 2026 S15.xlsx
+++ b/Plannings 2026 S15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E3C082B-4D13-4A71-87F5-FE6456285F1B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="145">
   <si>
     <t>Planning des salariés du 06/04/2026 au 12/04/2026</t>
   </si>
@@ -457,9 +457,6 @@
   </si>
   <si>
     <t>P100M // EDF // ANNIV</t>
-  </si>
-  <si>
-    <t>11:00/13:00</t>
   </si>
 </sst>
 </file>
@@ -469,7 +466,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -568,12 +565,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -618,7 +609,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -860,24 +851,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1051,12 +1029,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5354,30 +5326,118 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
       <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5409,10 +5469,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5440,23 +5500,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>85</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5484,23 +5544,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5528,32 +5632,208 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5574,30 +5854,30 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5618,21 +5898,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5660,287 +5940,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
+        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5968,59 +5984,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6265,94 +6237,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5743575" y="11049000"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="126" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39C2D579-1616-4A85-BE47-DAD747AE6A8D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19920857" y="13620750"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="127" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59FB2FAE-90D7-440E-A9EF-9EE92D31511D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13280571" y="14409964"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6734,7 +6618,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="49.7109375" customWidth="1"/>
@@ -7928,278 +7812,254 @@
       <c r="D80" s="18"/>
       <c r="E80" s="18"/>
       <c r="F80" s="18"/>
-      <c r="G80" s="18" t="s">
-        <v>16</v>
+      <c r="G80" s="54" t="s">
+        <v>59</v>
       </c>
       <c r="H80" s="19"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="61"/>
-      <c r="B81" s="27"/>
+      <c r="A81" s="25"/>
+      <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="62" t="s">
-        <v>145</v>
+      <c r="G81" s="55" t="s">
+        <v>89</v>
       </c>
       <c r="H81" s="26"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="61"/>
-      <c r="B82" s="27"/>
+      <c r="A82" s="25"/>
+      <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="52" t="s">
-        <v>59</v>
+      <c r="G82" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H82" s="26"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="25"/>
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="28"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
-      <c r="G83" s="55" t="s">
-        <v>89</v>
+      <c r="G83" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="H83" s="26"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="25"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H84" s="26"/>
+      <c r="A84" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B84" s="17"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="18"/>
+      <c r="H84" s="19"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="28"/>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H85" s="26"/>
+      <c r="A85" s="20"/>
+      <c r="B85" s="22"/>
+      <c r="C85" s="22"/>
+      <c r="D85" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="E85" s="22"/>
+      <c r="F85" s="22"/>
+      <c r="G85" s="22"/>
+      <c r="H85" s="23"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B86" s="17"/>
       <c r="C86" s="18"/>
-      <c r="D86" s="34" t="s">
-        <v>12</v>
-      </c>
+      <c r="D86" s="18"/>
       <c r="E86" s="18"/>
       <c r="F86" s="18"/>
-      <c r="G86" s="18"/>
+      <c r="G86" s="34" t="s">
+        <v>12</v>
+      </c>
       <c r="H86" s="19"/>
     </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="20"/>
-      <c r="B87" s="22"/>
-      <c r="C87" s="22"/>
-      <c r="D87" s="41" t="s">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="25"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H87" s="26"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="25"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="H88" s="26"/>
+    </row>
+    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="20"/>
+      <c r="B89" s="22"/>
+      <c r="C89" s="22"/>
+      <c r="D89" s="22"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="H89" s="23"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B90" s="17"/>
+      <c r="C90" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D90" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" s="18"/>
+      <c r="F90" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G90" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H90" s="19"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="25"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H91" s="26"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="25"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H92" s="26"/>
+    </row>
+    <row r="93" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="20"/>
+      <c r="B93" s="22"/>
+      <c r="C93" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D93" s="22"/>
+      <c r="E93" s="22"/>
+      <c r="F93" s="22"/>
+      <c r="G93" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H93" s="23"/>
+    </row>
+    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B94" s="31"/>
+      <c r="C94" s="30"/>
+      <c r="D94" s="30"/>
+      <c r="E94" s="30"/>
+      <c r="F94" s="30"/>
+      <c r="G94" s="30"/>
+      <c r="H94" s="32"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B95" s="17"/>
+      <c r="C95" s="18"/>
+      <c r="D95" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95" s="18"/>
+      <c r="F95" s="18"/>
+      <c r="G95" s="18"/>
+      <c r="H95" s="19"/>
+    </row>
+    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="20"/>
+      <c r="B96" s="22"/>
+      <c r="C96" s="22"/>
+      <c r="D96" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="E87" s="22"/>
-      <c r="F87" s="22"/>
-      <c r="G87" s="22"/>
-      <c r="H87" s="23"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="B88" s="17"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="18"/>
-      <c r="E88" s="18"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="H88" s="19"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="25"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="H89" s="26"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="25"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H90" s="26"/>
-    </row>
-    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="20"/>
-      <c r="B91" s="22"/>
-      <c r="C91" s="22"/>
-      <c r="D91" s="22"/>
-      <c r="E91" s="22"/>
-      <c r="F91" s="22"/>
-      <c r="G91" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="H91" s="23"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B92" s="17"/>
-      <c r="C92" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D92" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E92" s="18"/>
-      <c r="F92" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G92" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="H92" s="19"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="25"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G93" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="H93" s="26"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="25"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H94" s="26"/>
-    </row>
-    <row r="95" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="20"/>
-      <c r="B95" s="22"/>
-      <c r="C95" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D95" s="22"/>
-      <c r="E95" s="22"/>
-      <c r="F95" s="22"/>
-      <c r="G95" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="H95" s="23"/>
-    </row>
-    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="B96" s="31"/>
-      <c r="C96" s="30"/>
-      <c r="D96" s="30"/>
-      <c r="E96" s="30"/>
-      <c r="F96" s="30"/>
-      <c r="G96" s="30"/>
-      <c r="H96" s="32"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="B97" s="17"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="E97" s="18"/>
-      <c r="F97" s="18"/>
-      <c r="G97" s="18"/>
-      <c r="H97" s="19"/>
-    </row>
-    <row r="98" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="20"/>
-      <c r="B98" s="22"/>
-      <c r="C98" s="22"/>
-      <c r="D98" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="E98" s="22"/>
-      <c r="F98" s="22"/>
-      <c r="G98" s="22"/>
-      <c r="H98" s="23"/>
-    </row>
-    <row r="99" spans="1:8" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="33"/>
-      <c r="C99" s="33"/>
-      <c r="D99" s="33"/>
-      <c r="E99" s="33"/>
-      <c r="F99" s="33"/>
-      <c r="G99" s="33"/>
-      <c r="H99" s="33"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="22"/>
+      <c r="G96" s="22"/>
+      <c r="H96" s="23"/>
+    </row>
+    <row r="97" spans="2:8" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="33"/>
+      <c r="C97" s="33"/>
+      <c r="D97" s="33"/>
+      <c r="E97" s="33"/>
+      <c r="F97" s="33"/>
+      <c r="G97" s="33"/>
+      <c r="H97" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B99:H99"/>
+    <mergeCell ref="B97:H97"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="B47:H47"/>
     <mergeCell ref="B46:H46"/>
     <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B96:H96"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A91"/>
-    <mergeCell ref="A92:A95"/>
-    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="B94:H94"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A95:A96"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A64:A71"/>
     <mergeCell ref="A72:A73"/>
     <mergeCell ref="A74:A79"/>
-    <mergeCell ref="A80:A85"/>
+    <mergeCell ref="A80:A83"/>
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="A50:A53"/>
     <mergeCell ref="A54:A61"/>
@@ -8983,13 +8843,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDAB798-0440-4850-BA72-F263CA81D953}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{744CE1F1-CD27-4266-9A98-F6C54EF8FFEE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D713C6A8-9D75-4CA0-8563-0A53F6E83FDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F41EB0-F4AF-4816-9163-6C8ADF105326}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13671726-3036-4FB6-B875-2A77F871B70F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D7E64A4-E99B-45E4-820F-4A2C57506F77}"/>
 </file>
--- a/Plannings 2026 S15.xlsx
+++ b/Plannings 2026 S15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E3C082B-4D13-4A71-87F5-FE6456285F1B}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B1A2F48-B66D-4DB8-8FD3-4F3EF7B722E5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="147">
   <si>
     <t>Planning des salariés du 06/04/2026 au 12/04/2026</t>
   </si>
@@ -460,6 +460,9 @@
   </si>
   <si>
     <t>11:00/13:00</t>
+  </si>
+  <si>
+    <t>AIDE ANNIV</t>
   </si>
 </sst>
 </file>
@@ -7276,7 +7279,7 @@
       </c>
       <c r="G35" s="18"/>
       <c r="H35" s="48" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -8983,13 +8986,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDAB798-0440-4850-BA72-F263CA81D953}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5668D0B7-8B1F-4242-A97A-E161430D4FC9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D713C6A8-9D75-4CA0-8563-0A53F6E83FDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB8D50B-FFC7-443F-8B55-6231A31F1AC9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13671726-3036-4FB6-B875-2A77F871B70F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59680142-A99F-42CA-8DD9-EA8A289830D1}"/>
 </file>
--- a/Plannings 2026 S15.xlsx
+++ b/Plannings 2026 S15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B1A2F48-B66D-4DB8-8FD3-4F3EF7B722E5}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CED7B300-4950-4041-B478-8B05A8E045D4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="146">
   <si>
     <t>Planning des salariés du 06/04/2026 au 12/04/2026</t>
   </si>
@@ -340,9 +340,6 @@
   </si>
   <si>
     <t>09:45/11:00</t>
-  </si>
-  <si>
-    <t>09:45/19:00</t>
   </si>
   <si>
     <t>16:00/22:20</t>
@@ -6767,22 +6764,22 @@
     </row>
     <row r="3" spans="1:8" s="59" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="60" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="60" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="E3" s="60" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="60" t="s">
-        <v>140</v>
-      </c>
-      <c r="E3" s="60" t="s">
+      <c r="F3" s="60" t="s">
         <v>142</v>
       </c>
-      <c r="F3" s="60" t="s">
+      <c r="G3" s="60" t="s">
         <v>143</v>
-      </c>
-      <c r="G3" s="60" t="s">
-        <v>144</v>
       </c>
       <c r="H3" s="60" t="s">
         <v>59</v>
@@ -7279,7 +7276,7 @@
       </c>
       <c r="G35" s="18"/>
       <c r="H35" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -7480,14 +7477,14 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B50" s="17"/>
       <c r="C50" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="D50" s="43" t="s">
         <v>137</v>
-      </c>
-      <c r="D50" s="43" t="s">
-        <v>138</v>
       </c>
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
@@ -7512,7 +7509,7 @@
       <c r="A52" s="25"/>
       <c r="B52" s="1"/>
       <c r="C52" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D52" s="45" t="s">
         <v>67</v>
@@ -7866,12 +7863,12 @@
       <c r="E75" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F75" s="1" t="s">
-        <v>106</v>
+      <c r="F75" s="62" t="s">
+        <v>20</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -7892,7 +7889,7 @@
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="39" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -7916,7 +7913,7 @@
       <c r="C79" s="22"/>
       <c r="D79" s="22"/>
       <c r="E79" s="22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F79" s="22"/>
       <c r="G79" s="22"/>
@@ -7924,7 +7921,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B80" s="17"/>
       <c r="C80" s="18"/>
@@ -7944,7 +7941,7 @@
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="62" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H81" s="26"/>
     </row>
@@ -7992,13 +7989,13 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H85" s="26"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B86" s="17"/>
       <c r="C86" s="18"/>
@@ -8015,7 +8012,7 @@
       <c r="B87" s="22"/>
       <c r="C87" s="22"/>
       <c r="D87" s="41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E87" s="22"/>
       <c r="F87" s="22"/>
@@ -8024,7 +8021,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B88" s="17"/>
       <c r="C88" s="18"/>
@@ -8074,7 +8071,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B92" s="17"/>
       <c r="C92" s="34" t="s">
@@ -8103,10 +8100,10 @@
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G93" s="55" t="s">
         <v>116</v>
-      </c>
-      <c r="G93" s="55" t="s">
-        <v>117</v>
       </c>
       <c r="H93" s="26"/>
     </row>
@@ -8128,19 +8125,19 @@
       <c r="A95" s="20"/>
       <c r="B95" s="22"/>
       <c r="C95" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D95" s="22"/>
       <c r="E95" s="22"/>
       <c r="F95" s="22"/>
       <c r="G95" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H95" s="23"/>
     </row>
     <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B96" s="31"/>
       <c r="C96" s="30"/>
@@ -8152,7 +8149,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B97" s="17"/>
       <c r="C97" s="18"/>
@@ -8169,7 +8166,7 @@
       <c r="B98" s="22"/>
       <c r="C98" s="22"/>
       <c r="D98" s="41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E98" s="22"/>
       <c r="F98" s="22"/>
@@ -8236,7 +8233,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -8244,7 +8241,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -8255,16 +8252,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8643,7 +8640,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8660,7 +8657,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8677,7 +8674,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -8694,7 +8691,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -8711,7 +8708,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -8728,7 +8725,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -8778,21 +8775,21 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>101</v>
@@ -8800,18 +8797,18 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -8986,13 +8983,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5668D0B7-8B1F-4242-A97A-E161430D4FC9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A844723B-FCF5-4653-98D9-D98F0FF571D7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB8D50B-FFC7-443F-8B55-6231A31F1AC9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEAAA547-10C7-4892-8CEE-1E6E4797F670}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59680142-A99F-42CA-8DD9-EA8A289830D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F0AE934-E265-4675-9E1F-FACF80F4BF3B}"/>
 </file>
--- a/Plannings 2026 S15.xlsx
+++ b/Plannings 2026 S15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CED7B300-4950-4041-B478-8B05A8E045D4}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22DB6E1F-BFAC-4331-96FE-C4CA270B93DF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="150">
   <si>
     <t>Planning des salariés du 06/04/2026 au 12/04/2026</t>
   </si>
@@ -459,7 +459,19 @@
     <t>11:00/13:00</t>
   </si>
   <si>
-    <t>AIDE ANNIV</t>
+    <t>13:30/15:30</t>
+  </si>
+  <si>
+    <t>15:30/17:30</t>
+  </si>
+  <si>
+    <t>AIDE - ANNIV</t>
+  </si>
+  <si>
+    <t>10:45/12:45</t>
+  </si>
+  <si>
+    <t>12:45/13:45</t>
   </si>
 </sst>
 </file>
@@ -1012,9 +1024,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1057,6 +1066,9 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6353,6 +6365,270 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13280571" y="14409964"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="128" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3564BC9F-8A55-4E22-9359-3640C2944806}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4267200" y="8963025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="129" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2C731C1-6E27-403A-90E1-95812CEEFA5C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4267200" y="9344025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="130" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF47EE2F-0C3C-4D18-B29C-508C0234C984}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4267200" y="9725025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="131" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D38D706-5873-4210-AF53-2A51281B9576}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4267200" y="21155025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="132" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A52D836-DD8A-4F30-8D59-3AEA393EBAE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4267200" y="21536025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="133" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16A75A70-092E-4BEF-AF37-64BAEE0BA7D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4267200" y="21917025"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6737,7 +7013,7 @@
   <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="49.7109375" customWidth="1"/>
+    <col min="1" max="8" width="51.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6762,26 +7038,26 @@
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
     </row>
-    <row r="3" spans="1:8" s="59" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="60" t="s">
+    <row r="3" spans="1:8" s="58" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="59" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="60" t="s">
+      <c r="D3" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="F3" s="60" t="s">
+      <c r="F3" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="G3" s="60" t="s">
+      <c r="G3" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="H3" s="60" t="s">
+      <c r="H3" s="59" t="s">
         <v>59</v>
       </c>
     </row>
@@ -7052,7 +7328,7 @@
       <c r="B21" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="57" t="s">
         <v>38</v>
       </c>
       <c r="D21" s="34" t="s">
@@ -7061,7 +7337,7 @@
       <c r="E21" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="58" t="s">
+      <c r="F21" s="57" t="s">
         <v>38</v>
       </c>
       <c r="G21" s="38" t="s">
@@ -7074,7 +7350,7 @@
       <c r="B22" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="57" t="s">
+      <c r="C22" s="56" t="s">
         <v>42</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -7083,7 +7359,7 @@
       <c r="E22" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="F22" s="57" t="s">
+      <c r="F22" s="56" t="s">
         <v>45</v>
       </c>
       <c r="G22" s="39" t="s">
@@ -7100,7 +7376,7 @@
       <c r="D23" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="56" t="s">
+      <c r="E23" s="55" t="s">
         <v>38</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -7118,7 +7394,7 @@
       <c r="D24" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="57" t="s">
+      <c r="E24" s="56" t="s">
         <v>50</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -7136,7 +7412,7 @@
       <c r="D25" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="57"/>
+      <c r="E25" s="56"/>
       <c r="F25" s="1"/>
       <c r="G25" s="39"/>
       <c r="H25" s="26"/>
@@ -7150,7 +7426,7 @@
       <c r="D26" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="57"/>
+      <c r="E26" s="56"/>
       <c r="F26" s="1"/>
       <c r="G26" s="39"/>
       <c r="H26" s="26"/>
@@ -7158,13 +7434,13 @@
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
       <c r="B27" s="35"/>
-      <c r="C27" s="56" t="s">
+      <c r="C27" s="55" t="s">
         <v>38</v>
       </c>
       <c r="D27" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="E27" s="57"/>
+      <c r="E27" s="56"/>
       <c r="F27" s="1"/>
       <c r="G27" s="39"/>
       <c r="H27" s="26"/>
@@ -7172,13 +7448,13 @@
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
       <c r="B28" s="35"/>
-      <c r="C28" s="57" t="s">
+      <c r="C28" s="56" t="s">
         <v>54</v>
       </c>
       <c r="D28" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="57"/>
+      <c r="E28" s="56"/>
       <c r="F28" s="1"/>
       <c r="G28" s="39"/>
       <c r="H28" s="26"/>
@@ -7190,7 +7466,7 @@
         <v>47</v>
       </c>
       <c r="D29" s="35"/>
-      <c r="E29" s="57"/>
+      <c r="E29" s="56"/>
       <c r="F29" s="1"/>
       <c r="G29" s="39"/>
       <c r="H29" s="26"/>
@@ -7202,7 +7478,7 @@
         <v>56</v>
       </c>
       <c r="D30" s="35"/>
-      <c r="E30" s="57"/>
+      <c r="E30" s="56"/>
       <c r="F30" s="1"/>
       <c r="G30" s="39"/>
       <c r="H30" s="26"/>
@@ -7214,7 +7490,7 @@
         <v>38</v>
       </c>
       <c r="D31" s="35"/>
-      <c r="E31" s="57"/>
+      <c r="E31" s="56"/>
       <c r="F31" s="1"/>
       <c r="G31" s="39"/>
       <c r="H31" s="26"/>
@@ -7226,7 +7502,7 @@
         <v>41</v>
       </c>
       <c r="D32" s="35"/>
-      <c r="E32" s="57"/>
+      <c r="E32" s="56"/>
       <c r="F32" s="1"/>
       <c r="G32" s="39"/>
       <c r="H32" s="26"/>
@@ -7275,8 +7551,8 @@
         <v>12</v>
       </c>
       <c r="G35" s="18"/>
-      <c r="H35" s="48" t="s">
-        <v>145</v>
+      <c r="H35" s="51" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -7295,8 +7571,8 @@
         <v>62</v>
       </c>
       <c r="G36" s="1"/>
-      <c r="H36" s="49" t="s">
-        <v>63</v>
+      <c r="H36" s="54" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -7313,8 +7589,8 @@
         <v>16</v>
       </c>
       <c r="G37" s="1"/>
-      <c r="H37" s="29" t="s">
-        <v>16</v>
+      <c r="H37" s="51" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -7331,8 +7607,8 @@
         <v>65</v>
       </c>
       <c r="G38" s="1"/>
-      <c r="H38" s="26" t="s">
-        <v>66</v>
+      <c r="H38" s="54" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -7347,7 +7623,9 @@
       <c r="E39" s="39"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-      <c r="H39" s="26"/>
+      <c r="H39" s="62" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="25"/>
@@ -7361,7 +7639,9 @@
       <c r="E40" s="39"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="26"/>
+      <c r="H40" s="61" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="25"/>
@@ -7373,7 +7653,7 @@
       <c r="E41" s="39"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="26"/>
+      <c r="H41" s="61"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="20"/>
@@ -7385,7 +7665,7 @@
       <c r="E42" s="40"/>
       <c r="F42" s="22"/>
       <c r="G42" s="22"/>
-      <c r="H42" s="23"/>
+      <c r="H42" s="61"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
@@ -7567,7 +7847,7 @@
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
-      <c r="H56" s="50" t="s">
+      <c r="H56" s="49" t="s">
         <v>59</v>
       </c>
     </row>
@@ -7579,7 +7859,7 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
-      <c r="H57" s="49" t="s">
+      <c r="H57" s="48" t="s">
         <v>83</v>
       </c>
     </row>
@@ -7615,7 +7895,7 @@
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="50" t="s">
+      <c r="H60" s="49" t="s">
         <v>59</v>
       </c>
     </row>
@@ -7627,7 +7907,7 @@
       <c r="E61" s="22"/>
       <c r="F61" s="22"/>
       <c r="G61" s="22"/>
-      <c r="H61" s="51" t="s">
+      <c r="H61" s="50" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7782,7 +8062,7 @@
       <c r="D70" s="44"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="52" t="s">
+      <c r="G70" s="51" t="s">
         <v>59</v>
       </c>
       <c r="H70" s="26"/>
@@ -7794,7 +8074,7 @@
       <c r="D71" s="46"/>
       <c r="E71" s="22"/>
       <c r="F71" s="22"/>
-      <c r="G71" s="53" t="s">
+      <c r="G71" s="52" t="s">
         <v>99</v>
       </c>
       <c r="H71" s="23"/>
@@ -7863,7 +8143,7 @@
       <c r="E75" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F75" s="62" t="s">
+      <c r="F75" s="61" t="s">
         <v>20</v>
       </c>
       <c r="G75" s="1"/>
@@ -7931,31 +8211,37 @@
       <c r="G80" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="H80" s="19"/>
+      <c r="H80" s="51" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="61"/>
+      <c r="A81" s="60"/>
       <c r="B81" s="27"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="62" t="s">
+      <c r="G81" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="H81" s="26"/>
+      <c r="H81" s="54" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="61"/>
+      <c r="A82" s="60"/>
       <c r="B82" s="27"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="52" t="s">
+      <c r="G82" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="H82" s="26"/>
+      <c r="H82" s="62" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="25"/>
@@ -7964,10 +8250,12 @@
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
-      <c r="G83" s="55" t="s">
+      <c r="G83" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="H83" s="26"/>
+      <c r="H83" s="61" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="25"/>
@@ -7979,7 +8267,9 @@
       <c r="G84" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H84" s="26"/>
+      <c r="H84" s="51" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="28"/>
@@ -7991,7 +8281,9 @@
       <c r="G85" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H85" s="26"/>
+      <c r="H85" s="54" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="16" t="s">
@@ -8084,7 +8376,7 @@
       <c r="F92" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G92" s="54" t="s">
+      <c r="G92" s="53" t="s">
         <v>59</v>
       </c>
       <c r="H92" s="19"/>
@@ -8102,7 +8394,7 @@
       <c r="F93" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G93" s="55" t="s">
+      <c r="G93" s="54" t="s">
         <v>116</v>
       </c>
       <c r="H93" s="26"/>
@@ -8216,7 +8508,7 @@
     <mergeCell ref="A8:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="32" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -8983,13 +9275,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A844723B-FCF5-4653-98D9-D98F0FF571D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{040A8036-5E89-46C4-89CD-6C849419C574}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEAAA547-10C7-4892-8CEE-1E6E4797F670}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E9CBB77-BA74-4A25-9D8C-8104603F6CB9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F0AE934-E265-4675-9E1F-FACF80F4BF3B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B651C2CF-A054-4F4B-9233-C6BF1F90BBF7}"/>
 </file>
--- a/Plannings 2026 S15.xlsx
+++ b/Plannings 2026 S15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22DB6E1F-BFAC-4331-96FE-C4CA270B93DF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="145">
   <si>
     <t>Planning des salariés du 06/04/2026 au 12/04/2026</t>
   </si>
@@ -342,6 +342,9 @@
     <t>09:45/11:00</t>
   </si>
   <si>
+    <t>09:45/19:00</t>
+  </si>
+  <si>
     <t>16:00/22:20</t>
   </si>
   <si>
@@ -454,24 +457,6 @@
   </si>
   <si>
     <t>P100M // EDF // ANNIV</t>
-  </si>
-  <si>
-    <t>11:00/13:00</t>
-  </si>
-  <si>
-    <t>13:30/15:30</t>
-  </si>
-  <si>
-    <t>15:30/17:30</t>
-  </si>
-  <si>
-    <t>AIDE - ANNIV</t>
-  </si>
-  <si>
-    <t>10:45/12:45</t>
-  </si>
-  <si>
-    <t>12:45/13:45</t>
   </si>
 </sst>
 </file>
@@ -481,7 +466,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -580,12 +565,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -630,7 +609,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -872,24 +851,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1024,6 +990,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1060,15 +1029,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5366,30 +5326,118 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
       <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5421,10 +5469,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5452,23 +5500,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>85</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5496,23 +5544,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5540,32 +5632,208 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5586,30 +5854,30 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5630,21 +5898,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5672,287 +5940,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
+        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5980,59 +5984,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6277,358 +6237,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5743575" y="11049000"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="126" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39C2D579-1616-4A85-BE47-DAD747AE6A8D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19920857" y="13620750"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="127" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59FB2FAE-90D7-440E-A9EF-9EE92D31511D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13280571" y="14409964"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="128" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3564BC9F-8A55-4E22-9359-3640C2944806}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4267200" y="8963025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="129" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2C731C1-6E27-403A-90E1-95812CEEFA5C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4267200" y="9344025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="130" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF47EE2F-0C3C-4D18-B29C-508C0234C984}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4267200" y="9725025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="131" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D38D706-5873-4210-AF53-2A51281B9576}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4267200" y="21155025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="132" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A52D836-DD8A-4F30-8D59-3AEA393EBAE9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4267200" y="21536025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="133" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16A75A70-092E-4BEF-AF37-64BAEE0BA7D7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4267200" y="21917025"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7010,10 +6618,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="51.42578125" customWidth="1"/>
+    <col min="1" max="8" width="49.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7038,26 +6646,26 @@
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
     </row>
-    <row r="3" spans="1:8" s="58" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="59" t="s">
+    <row r="3" spans="1:8" s="59" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="60" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="E3" s="59" t="s">
-        <v>141</v>
-      </c>
-      <c r="F3" s="59" t="s">
+      <c r="E3" s="60" t="s">
         <v>142</v>
       </c>
-      <c r="G3" s="59" t="s">
+      <c r="F3" s="60" t="s">
         <v>143</v>
       </c>
-      <c r="H3" s="59" t="s">
+      <c r="G3" s="60" t="s">
+        <v>144</v>
+      </c>
+      <c r="H3" s="60" t="s">
         <v>59</v>
       </c>
     </row>
@@ -7328,7 +6936,7 @@
       <c r="B21" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C21" s="58" t="s">
         <v>38</v>
       </c>
       <c r="D21" s="34" t="s">
@@ -7337,7 +6945,7 @@
       <c r="E21" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="57" t="s">
+      <c r="F21" s="58" t="s">
         <v>38</v>
       </c>
       <c r="G21" s="38" t="s">
@@ -7350,7 +6958,7 @@
       <c r="B22" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="56" t="s">
+      <c r="C22" s="57" t="s">
         <v>42</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -7359,7 +6967,7 @@
       <c r="E22" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="F22" s="56" t="s">
+      <c r="F22" s="57" t="s">
         <v>45</v>
       </c>
       <c r="G22" s="39" t="s">
@@ -7376,7 +6984,7 @@
       <c r="D23" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="55" t="s">
+      <c r="E23" s="56" t="s">
         <v>38</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -7394,7 +7002,7 @@
       <c r="D24" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="56" t="s">
+      <c r="E24" s="57" t="s">
         <v>50</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -7412,7 +7020,7 @@
       <c r="D25" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="56"/>
+      <c r="E25" s="57"/>
       <c r="F25" s="1"/>
       <c r="G25" s="39"/>
       <c r="H25" s="26"/>
@@ -7426,7 +7034,7 @@
       <c r="D26" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="56"/>
+      <c r="E26" s="57"/>
       <c r="F26" s="1"/>
       <c r="G26" s="39"/>
       <c r="H26" s="26"/>
@@ -7434,13 +7042,13 @@
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
       <c r="B27" s="35"/>
-      <c r="C27" s="55" t="s">
+      <c r="C27" s="56" t="s">
         <v>38</v>
       </c>
       <c r="D27" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="E27" s="56"/>
+      <c r="E27" s="57"/>
       <c r="F27" s="1"/>
       <c r="G27" s="39"/>
       <c r="H27" s="26"/>
@@ -7448,13 +7056,13 @@
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
       <c r="B28" s="35"/>
-      <c r="C28" s="56" t="s">
+      <c r="C28" s="57" t="s">
         <v>54</v>
       </c>
       <c r="D28" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="56"/>
+      <c r="E28" s="57"/>
       <c r="F28" s="1"/>
       <c r="G28" s="39"/>
       <c r="H28" s="26"/>
@@ -7466,7 +7074,7 @@
         <v>47</v>
       </c>
       <c r="D29" s="35"/>
-      <c r="E29" s="56"/>
+      <c r="E29" s="57"/>
       <c r="F29" s="1"/>
       <c r="G29" s="39"/>
       <c r="H29" s="26"/>
@@ -7478,7 +7086,7 @@
         <v>56</v>
       </c>
       <c r="D30" s="35"/>
-      <c r="E30" s="56"/>
+      <c r="E30" s="57"/>
       <c r="F30" s="1"/>
       <c r="G30" s="39"/>
       <c r="H30" s="26"/>
@@ -7490,7 +7098,7 @@
         <v>38</v>
       </c>
       <c r="D31" s="35"/>
-      <c r="E31" s="56"/>
+      <c r="E31" s="57"/>
       <c r="F31" s="1"/>
       <c r="G31" s="39"/>
       <c r="H31" s="26"/>
@@ -7502,7 +7110,7 @@
         <v>41</v>
       </c>
       <c r="D32" s="35"/>
-      <c r="E32" s="56"/>
+      <c r="E32" s="57"/>
       <c r="F32" s="1"/>
       <c r="G32" s="39"/>
       <c r="H32" s="26"/>
@@ -7551,7 +7159,7 @@
         <v>12</v>
       </c>
       <c r="G35" s="18"/>
-      <c r="H35" s="51" t="s">
+      <c r="H35" s="48" t="s">
         <v>59</v>
       </c>
     </row>
@@ -7571,8 +7179,8 @@
         <v>62</v>
       </c>
       <c r="G36" s="1"/>
-      <c r="H36" s="54" t="s">
-        <v>145</v>
+      <c r="H36" s="49" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -7589,8 +7197,8 @@
         <v>16</v>
       </c>
       <c r="G37" s="1"/>
-      <c r="H37" s="51" t="s">
-        <v>147</v>
+      <c r="H37" s="29" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -7607,8 +7215,8 @@
         <v>65</v>
       </c>
       <c r="G38" s="1"/>
-      <c r="H38" s="54" t="s">
-        <v>146</v>
+      <c r="H38" s="26" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -7623,9 +7231,7 @@
       <c r="E39" s="39"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-      <c r="H39" s="62" t="s">
-        <v>16</v>
-      </c>
+      <c r="H39" s="26"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="25"/>
@@ -7639,9 +7245,7 @@
       <c r="E40" s="39"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="61" t="s">
-        <v>66</v>
-      </c>
+      <c r="H40" s="26"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="25"/>
@@ -7653,7 +7257,7 @@
       <c r="E41" s="39"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="61"/>
+      <c r="H41" s="26"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="20"/>
@@ -7665,7 +7269,7 @@
       <c r="E42" s="40"/>
       <c r="F42" s="22"/>
       <c r="G42" s="22"/>
-      <c r="H42" s="61"/>
+      <c r="H42" s="23"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
@@ -7757,14 +7361,14 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B50" s="17"/>
       <c r="C50" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D50" s="43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
@@ -7789,7 +7393,7 @@
       <c r="A52" s="25"/>
       <c r="B52" s="1"/>
       <c r="C52" s="45" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D52" s="45" t="s">
         <v>67</v>
@@ -7847,7 +7451,7 @@
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
-      <c r="H56" s="49" t="s">
+      <c r="H56" s="50" t="s">
         <v>59</v>
       </c>
     </row>
@@ -7859,7 +7463,7 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
-      <c r="H57" s="48" t="s">
+      <c r="H57" s="49" t="s">
         <v>83</v>
       </c>
     </row>
@@ -7895,7 +7499,7 @@
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="49" t="s">
+      <c r="H60" s="50" t="s">
         <v>59</v>
       </c>
     </row>
@@ -7907,7 +7511,7 @@
       <c r="E61" s="22"/>
       <c r="F61" s="22"/>
       <c r="G61" s="22"/>
-      <c r="H61" s="50" t="s">
+      <c r="H61" s="51" t="s">
         <v>63</v>
       </c>
     </row>
@@ -8062,7 +7666,7 @@
       <c r="D70" s="44"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="51" t="s">
+      <c r="G70" s="52" t="s">
         <v>59</v>
       </c>
       <c r="H70" s="26"/>
@@ -8074,7 +7678,7 @@
       <c r="D71" s="46"/>
       <c r="E71" s="22"/>
       <c r="F71" s="22"/>
-      <c r="G71" s="52" t="s">
+      <c r="G71" s="53" t="s">
         <v>99</v>
       </c>
       <c r="H71" s="23"/>
@@ -8143,12 +7747,12 @@
       <c r="E75" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F75" s="61" t="s">
-        <v>20</v>
+      <c r="F75" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -8169,7 +7773,7 @@
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="39" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -8193,7 +7797,7 @@
       <c r="C79" s="22"/>
       <c r="D79" s="22"/>
       <c r="E79" s="22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F79" s="22"/>
       <c r="G79" s="22"/>
@@ -8201,297 +7805,261 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B80" s="17"/>
       <c r="C80" s="18"/>
       <c r="D80" s="18"/>
       <c r="E80" s="18"/>
       <c r="F80" s="18"/>
-      <c r="G80" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="H80" s="51" t="s">
+      <c r="G80" s="54" t="s">
         <v>59</v>
       </c>
+      <c r="H80" s="19"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="60"/>
-      <c r="B81" s="27"/>
+      <c r="A81" s="25"/>
+      <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="61" t="s">
-        <v>144</v>
-      </c>
-      <c r="H81" s="54" t="s">
-        <v>148</v>
-      </c>
+      <c r="G81" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="H81" s="26"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="60"/>
-      <c r="B82" s="27"/>
+      <c r="A82" s="25"/>
+      <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="H82" s="62" t="s">
+      <c r="G82" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="25"/>
+      <c r="H82" s="26"/>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="28"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
-      <c r="G83" s="54" t="s">
-        <v>89</v>
-      </c>
-      <c r="H83" s="61" t="s">
-        <v>149</v>
-      </c>
+      <c r="G83" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H83" s="26"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="25"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H84" s="51" t="s">
-        <v>59</v>
-      </c>
+      <c r="A84" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B84" s="17"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="18"/>
+      <c r="H84" s="19"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="28"/>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H85" s="54" t="s">
-        <v>89</v>
-      </c>
+      <c r="A85" s="20"/>
+      <c r="B85" s="22"/>
+      <c r="C85" s="22"/>
+      <c r="D85" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="E85" s="22"/>
+      <c r="F85" s="22"/>
+      <c r="G85" s="22"/>
+      <c r="H85" s="23"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="16" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B86" s="17"/>
       <c r="C86" s="18"/>
-      <c r="D86" s="34" t="s">
-        <v>12</v>
-      </c>
+      <c r="D86" s="18"/>
       <c r="E86" s="18"/>
       <c r="F86" s="18"/>
-      <c r="G86" s="18"/>
+      <c r="G86" s="34" t="s">
+        <v>12</v>
+      </c>
       <c r="H86" s="19"/>
     </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="20"/>
-      <c r="B87" s="22"/>
-      <c r="C87" s="22"/>
-      <c r="D87" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="E87" s="22"/>
-      <c r="F87" s="22"/>
-      <c r="G87" s="22"/>
-      <c r="H87" s="23"/>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="25"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H87" s="26"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="16" t="s">
+      <c r="A88" s="25"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="H88" s="26"/>
+    </row>
+    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="20"/>
+      <c r="B89" s="22"/>
+      <c r="C89" s="22"/>
+      <c r="D89" s="22"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="H89" s="23"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B90" s="17"/>
+      <c r="C90" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D90" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" s="18"/>
+      <c r="F90" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G90" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H90" s="19"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="25"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H91" s="26"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="25"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H92" s="26"/>
+    </row>
+    <row r="93" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="20"/>
+      <c r="B93" s="22"/>
+      <c r="C93" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D93" s="22"/>
+      <c r="E93" s="22"/>
+      <c r="F93" s="22"/>
+      <c r="G93" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H93" s="23"/>
+    </row>
+    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B94" s="31"/>
+      <c r="C94" s="30"/>
+      <c r="D94" s="30"/>
+      <c r="E94" s="30"/>
+      <c r="F94" s="30"/>
+      <c r="G94" s="30"/>
+      <c r="H94" s="32"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B95" s="17"/>
+      <c r="C95" s="18"/>
+      <c r="D95" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95" s="18"/>
+      <c r="F95" s="18"/>
+      <c r="G95" s="18"/>
+      <c r="H95" s="19"/>
+    </row>
+    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="20"/>
+      <c r="B96" s="22"/>
+      <c r="C96" s="22"/>
+      <c r="D96" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="B88" s="17"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="18"/>
-      <c r="E88" s="18"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="H88" s="19"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="25"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="H89" s="26"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="25"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H90" s="26"/>
-    </row>
-    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="20"/>
-      <c r="B91" s="22"/>
-      <c r="C91" s="22"/>
-      <c r="D91" s="22"/>
-      <c r="E91" s="22"/>
-      <c r="F91" s="22"/>
-      <c r="G91" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="H91" s="23"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="B92" s="17"/>
-      <c r="C92" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D92" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E92" s="18"/>
-      <c r="F92" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G92" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="H92" s="19"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="25"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G93" s="54" t="s">
-        <v>116</v>
-      </c>
-      <c r="H93" s="26"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="25"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H94" s="26"/>
-    </row>
-    <row r="95" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="20"/>
-      <c r="B95" s="22"/>
-      <c r="C95" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="D95" s="22"/>
-      <c r="E95" s="22"/>
-      <c r="F95" s="22"/>
-      <c r="G95" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="H95" s="23"/>
-    </row>
-    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="B96" s="31"/>
-      <c r="C96" s="30"/>
-      <c r="D96" s="30"/>
-      <c r="E96" s="30"/>
-      <c r="F96" s="30"/>
-      <c r="G96" s="30"/>
-      <c r="H96" s="32"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="B97" s="17"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="E97" s="18"/>
-      <c r="F97" s="18"/>
-      <c r="G97" s="18"/>
-      <c r="H97" s="19"/>
-    </row>
-    <row r="98" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="20"/>
-      <c r="B98" s="22"/>
-      <c r="C98" s="22"/>
-      <c r="D98" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="E98" s="22"/>
-      <c r="F98" s="22"/>
-      <c r="G98" s="22"/>
-      <c r="H98" s="23"/>
-    </row>
-    <row r="99" spans="1:8" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="33"/>
-      <c r="C99" s="33"/>
-      <c r="D99" s="33"/>
-      <c r="E99" s="33"/>
-      <c r="F99" s="33"/>
-      <c r="G99" s="33"/>
-      <c r="H99" s="33"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="22"/>
+      <c r="G96" s="22"/>
+      <c r="H96" s="23"/>
+    </row>
+    <row r="97" spans="2:8" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="33"/>
+      <c r="C97" s="33"/>
+      <c r="D97" s="33"/>
+      <c r="E97" s="33"/>
+      <c r="F97" s="33"/>
+      <c r="G97" s="33"/>
+      <c r="H97" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B99:H99"/>
+    <mergeCell ref="B97:H97"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="B47:H47"/>
     <mergeCell ref="B46:H46"/>
     <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B96:H96"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A91"/>
-    <mergeCell ref="A92:A95"/>
-    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="B94:H94"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A95:A96"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A64:A71"/>
     <mergeCell ref="A72:A73"/>
     <mergeCell ref="A74:A79"/>
-    <mergeCell ref="A80:A85"/>
+    <mergeCell ref="A80:A83"/>
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="A50:A53"/>
     <mergeCell ref="A54:A61"/>
@@ -8508,7 +8076,7 @@
     <mergeCell ref="A8:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="32" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -8525,7 +8093,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -8533,7 +8101,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -8544,16 +8112,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8932,7 +8500,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8949,7 +8517,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8966,7 +8534,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -8983,7 +8551,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -9000,7 +8568,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -9017,7 +8585,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -9067,21 +8635,21 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>101</v>
@@ -9089,18 +8657,18 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -9275,13 +8843,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{040A8036-5E89-46C4-89CD-6C849419C574}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{744CE1F1-CD27-4266-9A98-F6C54EF8FFEE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E9CBB77-BA74-4A25-9D8C-8104603F6CB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F41EB0-F4AF-4816-9163-6C8ADF105326}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B651C2CF-A054-4F4B-9233-C6BF1F90BBF7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D7E64A4-E99B-45E4-820F-4A2C57506F77}"/>
 </file>
--- a/Plannings 2026 S15.xlsx
+++ b/Plannings 2026 S15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22DB6E1F-BFAC-4331-96FE-C4CA270B93DF}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{4B16CE52-039B-4D77-8B5C-7A7A29AECE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FED28E1-CFB0-4490-A0D7-557B22A2BB68}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -303,9 +303,6 @@
     <t>ENT-M</t>
   </si>
   <si>
-    <t>17:45/19:15</t>
-  </si>
-  <si>
     <t>09:30/12:30</t>
   </si>
   <si>
@@ -472,6 +469,9 @@
   </si>
   <si>
     <t>12:45/13:45</t>
+  </si>
+  <si>
+    <t>18:00/19:15</t>
   </si>
 </sst>
 </file>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="3" spans="1:8" s="58" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="E3" s="59" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="E3" s="59" t="s">
+      <c r="F3" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="G3" s="59" t="s">
         <v>142</v>
-      </c>
-      <c r="G3" s="59" t="s">
-        <v>143</v>
       </c>
       <c r="H3" s="59" t="s">
         <v>59</v>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="54" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="51" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="54" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -7757,14 +7757,14 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B50" s="17"/>
       <c r="C50" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="D50" s="43" t="s">
         <v>136</v>
-      </c>
-      <c r="D50" s="43" t="s">
-        <v>137</v>
       </c>
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
@@ -7789,7 +7789,7 @@
       <c r="A52" s="25"/>
       <c r="B52" s="1"/>
       <c r="C52" s="45" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D52" s="45" t="s">
         <v>67</v>
@@ -8011,15 +8011,15 @@
       <c r="C67" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>93</v>
+      <c r="D67" s="61" t="s">
+        <v>149</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H67" s="26"/>
     </row>
@@ -8028,7 +8028,7 @@
       <c r="B68" s="1"/>
       <c r="C68" s="44"/>
       <c r="D68" s="45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>16</v>
@@ -8044,14 +8044,14 @@
       <c r="B69" s="1"/>
       <c r="C69" s="44"/>
       <c r="D69" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H69" s="26"/>
     </row>
@@ -8075,13 +8075,13 @@
       <c r="E71" s="22"/>
       <c r="F71" s="22"/>
       <c r="G71" s="52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H71" s="23"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B72" s="17"/>
       <c r="C72" s="18"/>
@@ -8107,7 +8107,7 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B74" s="18" t="s">
         <v>16</v>
@@ -8132,23 +8132,23 @@
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="25"/>
       <c r="B75" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="F75" s="61" t="s">
         <v>20</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -8169,7 +8169,7 @@
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -8193,7 +8193,7 @@
       <c r="C79" s="22"/>
       <c r="D79" s="22"/>
       <c r="E79" s="22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F79" s="22"/>
       <c r="G79" s="22"/>
@@ -8201,7 +8201,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B80" s="17"/>
       <c r="C80" s="18"/>
@@ -8223,10 +8223,10 @@
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H81" s="54" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -8254,7 +8254,7 @@
         <v>89</v>
       </c>
       <c r="H83" s="61" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -8279,7 +8279,7 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H85" s="54" t="s">
         <v>89</v>
@@ -8287,7 +8287,7 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B86" s="17"/>
       <c r="C86" s="18"/>
@@ -8304,7 +8304,7 @@
       <c r="B87" s="22"/>
       <c r="C87" s="22"/>
       <c r="D87" s="41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E87" s="22"/>
       <c r="F87" s="22"/>
@@ -8313,7 +8313,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B88" s="17"/>
       <c r="C88" s="18"/>
@@ -8363,7 +8363,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B92" s="17"/>
       <c r="C92" s="34" t="s">
@@ -8392,10 +8392,10 @@
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G93" s="54" t="s">
         <v>115</v>
-      </c>
-      <c r="G93" s="54" t="s">
-        <v>116</v>
       </c>
       <c r="H93" s="26"/>
     </row>
@@ -8417,19 +8417,19 @@
       <c r="A95" s="20"/>
       <c r="B95" s="22"/>
       <c r="C95" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D95" s="22"/>
       <c r="E95" s="22"/>
       <c r="F95" s="22"/>
       <c r="G95" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H95" s="23"/>
     </row>
     <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B96" s="31"/>
       <c r="C96" s="30"/>
@@ -8441,7 +8441,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B97" s="17"/>
       <c r="C97" s="18"/>
@@ -8458,7 +8458,7 @@
       <c r="B98" s="22"/>
       <c r="C98" s="22"/>
       <c r="D98" s="41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E98" s="22"/>
       <c r="F98" s="22"/>
@@ -8525,7 +8525,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -8533,7 +8533,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -8544,16 +8544,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8898,7 +8898,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -8915,7 +8915,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -8932,7 +8932,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8949,7 +8949,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8966,7 +8966,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -8983,7 +8983,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -9000,7 +9000,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -9017,7 +9017,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -9067,40 +9067,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>127</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>131</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>133</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -9275,13 +9275,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{040A8036-5E89-46C4-89CD-6C849419C574}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8E7D34A-250A-4DAC-9442-BB1F485E7B74}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E9CBB77-BA74-4A25-9D8C-8104603F6CB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FCBCEF-217E-44C0-8B29-F811F19E7D30}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B651C2CF-A054-4F4B-9233-C6BF1F90BBF7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EDEE6DE-9DE6-4992-A85D-B42C658FFAE9}"/>
 </file>
--- a/Plannings 2026 S15.xlsx
+++ b/Plannings 2026 S15.xlsx
@@ -9275,13 +9275,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8E7D34A-250A-4DAC-9442-BB1F485E7B74}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D9C497D-14DB-4628-B9A9-282ED47A60A9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FCBCEF-217E-44C0-8B29-F811F19E7D30}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B34C423-76D1-4A68-94CC-DF0E5A73B91F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EDEE6DE-9DE6-4992-A85D-B42C658FFAE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F517F8A0-FCF2-4439-A637-EB81CEC2B69A}"/>
 </file>